--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1497,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1749,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1814,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1795,7 +1831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1231-79-CM26</t>
+          <t>5416-961-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,43 +1856,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.804.008-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6956.75</v>
+        <v>5596.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5416-961-CM26</t>
+          <t>1231-79-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,37 +1921,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.804.008-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5596.18</v>
+        <v>6956.75</v>
       </c>
     </row>
     <row r="25">
@@ -1978,7 +2022,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1208129-458-CM26</t>
+          <t>1375754-74-SE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2037,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,43 +2047,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>29216.36</v>
+        <v>10528.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5647-164-CM26</t>
+          <t>1208129-458-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2112,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2142,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10832.95</v>
+        <v>29216.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4081-303-CM26</t>
+          <t>5647-164-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,27 +2173,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2203,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>13249.78</v>
+        <v>10832.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1415864-29-CM26</t>
+          <t>4081-303-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,37 +2224,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2264,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6923.15</v>
+        <v>13249.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1461054-352-CM26</t>
+          <t>1415864-29-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,32 +2290,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2325,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>73103.75</v>
+        <v>6923.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2343-542-CM26</t>
+          <t>1461054-352-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2346,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2356,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2386,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>28074.77</v>
+        <v>73103.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057822-102-CM26</t>
+          <t>2343-542-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,43 +2417,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>24243.55</v>
+        <v>28074.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057822-113-CM26</t>
+          <t>1057822-102-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,13 +2512,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11377.04</v>
+        <v>24243.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2384-168-CM26</t>
+          <t>1057822-113-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,27 +2543,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2573,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22312.2</v>
+        <v>11377.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3474-519-CM26</t>
+          <t>2384-168-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,43 +2604,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>31726.47</v>
+        <v>22312.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2696-124-CM26</t>
+          <t>3474-519-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2659,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,27 +2669,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2699,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7476.59</v>
+        <v>31726.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>697224-49-CM26</t>
+          <t>2696-124-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2720,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,17 +2730,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2704,13 +2760,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9170.110000000001</v>
+        <v>7476.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1389183-606-CM26</t>
+          <t>697224-49-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,17 +2791,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2765,13 +2821,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>24468.88</v>
+        <v>9170.110000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1485217-156-CM26</t>
+          <t>1389183-606-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2842,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2852,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BASTIAN ANDRES PIZARRO LEON</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>17.203.260-5</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2882,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5401.18</v>
+        <v>24468.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1305543-89-CM26</t>
+          <t>1485217-156-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2913,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BASTIAN ANDRES PIZARRO LEON</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>17.203.260-5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8539.959999999999</v>
+        <v>5401.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2173-239-CM26</t>
+          <t>1305543-89-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2968,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,43 +2978,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9571.030000000001</v>
+        <v>8539.959999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5510-92-CM26</t>
+          <t>2173-239-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +3043,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3058,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3073,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>9259.51</v>
+        <v>9571.030000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057822-121-CM26</t>
+          <t>5510-92-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3094,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,43 +3104,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6909.92</v>
+        <v>9259.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5586-3380-CM26</t>
+          <t>1057822-121-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,43 +3169,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7852.16</v>
+        <v>6909.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45-233-CM26</t>
+          <t>5586-3380-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3234,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12845.81</v>
+        <v>7852.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1232565-314-CM26</t>
+          <t>45-233-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,27 +3295,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3325,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5654.99</v>
+        <v>12845.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1075718-55-CM26</t>
+          <t>1232565-314-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3346,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,97 +3356,170 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8151.36</v>
+        <v>5654.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>1075718-55-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>8151.36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>1775-52-CM26</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>60.804.004-8</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>15678.95</v>
       </c>
     </row>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1968-2232-CM26</t>
+          <t>4404-221-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,48 +1164,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13293.25</v>
+        <v>26391.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1271359-244-CM26</t>
+          <t>1968-2232-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1230,27 +1234,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1260,7 +1264,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>33241.75</v>
+        <v>13293.25</v>
       </c>
     </row>
     <row r="14">
@@ -1327,7 +1331,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1867-228-CM26</t>
+          <t>1271359-244-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1342,22 +1346,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1382,13 +1386,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9495.08</v>
+        <v>33241.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707422-152-CM26</t>
+          <t>1867-228-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1413,27 +1417,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1443,13 +1447,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9601.82</v>
+        <v>9495.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5358-222-CM26</t>
+          <t>707422-152-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1474,47 +1478,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.938-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11204.03</v>
+        <v>9601.82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2345-434-CM26</t>
+          <t>5358-222-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35843.37</v>
+        <v>11204.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1410-818-CM26</t>
+          <t>2345-434-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1594,47 +1594,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17149.16</v>
+        <v>35843.37</v>
       </c>
     </row>
     <row r="20">
@@ -1831,7 +1835,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5416-961-CM26</t>
+          <t>1410-818-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,51 +1850,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5596.18</v>
+        <v>17149.16</v>
       </c>
     </row>
     <row r="24">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1961,7 +1961,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5626-463-CM26</t>
+          <t>5416-961-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1981,48 +1981,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7346.99</v>
+        <v>5596.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1375754-74-SE26</t>
+          <t>5626-463-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2047,47 +2051,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.981.260-3</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.042.830-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10528.24</v>
+        <v>7346.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1208129-458-CM26</t>
+          <t>1375754-74-SE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2112,43 +2112,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>29216.36</v>
+        <v>10528.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5647-164-CM26</t>
+          <t>1208129-458-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2173,27 +2177,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2203,13 +2207,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10832.95</v>
+        <v>29216.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4081-303-CM26</t>
+          <t>5647-164-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2229,32 +2233,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2264,13 +2268,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13249.78</v>
+        <v>10832.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1415864-29-CM26</t>
+          <t>4081-303-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2285,37 +2289,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2325,13 +2329,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6923.15</v>
+        <v>13249.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1461054-352-CM26</t>
+          <t>1415864-29-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2351,32 +2355,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2386,13 +2390,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>73103.75</v>
+        <v>6923.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2343-542-CM26</t>
+          <t>1461054-352-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2407,7 +2411,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2417,41 +2421,37 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>28074.77</v>
+        <v>73103.75</v>
       </c>
     </row>
     <row r="33">
@@ -2705,7 +2705,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2696-124-CM26</t>
+          <t>2343-542-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2730,43 +2730,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7476.59</v>
+        <v>28074.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>697224-49-CM26</t>
+          <t>2696-124-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2781,7 +2785,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2791,17 +2795,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2821,7 +2825,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9170.110000000001</v>
+        <v>7476.59</v>
       </c>
     </row>
     <row r="39">
@@ -2888,7 +2892,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1485217-156-CM26</t>
+          <t>697224-49-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2903,7 +2907,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2913,12 +2917,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,32 +2932,28 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BASTIAN ANDRES PIZARRO LEON</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>17.203.260-5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5401.18</v>
+        <v>9170.110000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1305543-89-CM26</t>
+          <t>1485217-156-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2978,47 +2978,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BASTIAN ANDRES PIZARRO LEON</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17.203.260-5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8539.959999999999</v>
+        <v>5401.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2173-239-CM26</t>
+          <t>1305543-89-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3043,43 +3043,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>9571.030000000001</v>
+        <v>8539.959999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5510-92-CM26</t>
+          <t>2173-239-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3104,12 +3108,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3119,32 +3123,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>9259.51</v>
+        <v>9571.030000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057822-121-CM26</t>
+          <t>5510-92-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3169,27 +3169,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6909.92</v>
+        <v>9259.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5586-3380-CM26</t>
+          <t>1261592-1234-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3234,43 +3234,47 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7852.16</v>
+        <v>9647.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45-233-CM26</t>
+          <t>1057822-121-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3285,7 +3289,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3295,43 +3299,47 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12845.81</v>
+        <v>6909.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1232565-314-CM26</t>
+          <t>5586-3380-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3346,7 +3354,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3356,47 +3364,43 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5654.99</v>
+        <v>7852.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1075718-55-CM26</t>
+          <t>45-233-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3411,7 +3415,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3421,106 +3425,297 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8151.36</v>
+        <v>12845.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>1232565-314-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>5654.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1075718-55-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>8151.36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>1775-52-CM26</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>60.804.004-8</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
         <v>15678.95</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1059240-60-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>9464.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/sep-2026.xlsx
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
